--- a/research/traditional_assets/database/data/south_africa/south_africa_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/south_africa/south_africa_insurance_prop_cas.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.06559999999999999</v>
+        <v>0.0555</v>
       </c>
       <c r="E2">
-        <v>-0.0646</v>
+        <v>0.122</v>
       </c>
       <c r="G2">
-        <v>0.06247309256158813</v>
+        <v>0.1310240963855422</v>
       </c>
       <c r="H2">
-        <v>0.06247309256158813</v>
+        <v>0.1310240963855422</v>
       </c>
       <c r="I2">
-        <v>0.08567328390337239</v>
+        <v>0.09063037865748709</v>
       </c>
       <c r="J2">
-        <v>0.06834053860500226</v>
+        <v>0.07103858251643462</v>
       </c>
       <c r="K2">
-        <v>102.9</v>
+        <v>137.9</v>
       </c>
       <c r="L2">
-        <v>0.04922267400143507</v>
+        <v>0.07417168674698796</v>
       </c>
       <c r="M2">
-        <v>43.3887</v>
+        <v>146.6</v>
       </c>
       <c r="N2">
-        <v>0.02280135582531925</v>
+        <v>0.08608338226658838</v>
       </c>
       <c r="O2">
-        <v>0.4216588921282798</v>
+        <v>1.06308919506889</v>
       </c>
       <c r="P2">
-        <v>34.2087</v>
+        <v>136.6</v>
       </c>
       <c r="Q2">
-        <v>0.01797714015450103</v>
+        <v>0.08021139166177334</v>
       </c>
       <c r="R2">
-        <v>0.3324460641399417</v>
+        <v>0.9905728788977519</v>
       </c>
       <c r="S2">
-        <v>9.18</v>
+        <v>10</v>
       </c>
       <c r="T2">
-        <v>0.211575825042004</v>
+        <v>0.06821282401091405</v>
       </c>
       <c r="U2">
-        <v>320.5</v>
+        <v>273</v>
       </c>
       <c r="V2">
-        <v>0.1684271375269326</v>
+        <v>0.1603053435114504</v>
       </c>
       <c r="W2">
-        <v>0.1957762557077626</v>
+        <v>0.1979047072330655</v>
       </c>
       <c r="X2">
-        <v>0.07861119274588846</v>
+        <v>0.1238312207094029</v>
       </c>
       <c r="Y2">
-        <v>0.1171650629618741</v>
+        <v>0.07407348652366258</v>
       </c>
       <c r="Z2">
-        <v>4.954965631666271</v>
+        <v>2.753146749592774</v>
       </c>
       <c r="AA2">
-        <v>0.3386250200373482</v>
+        <v>0.1955796425508</v>
       </c>
       <c r="AB2">
-        <v>0.07271814185535347</v>
+        <v>0.1159769106107354</v>
       </c>
       <c r="AC2">
-        <v>0.2659068781819947</v>
+        <v>0.07960273194006463</v>
       </c>
       <c r="AD2">
-        <v>299</v>
+        <v>245.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>299</v>
+        <v>245.1</v>
       </c>
       <c r="AG2">
-        <v>-21.5</v>
+        <v>-27.90000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.135791816158772</v>
+        <v>0.1258148965658847</v>
       </c>
       <c r="AI2">
-        <v>0.2863710372569678</v>
+        <v>0.2752695417789757</v>
       </c>
       <c r="AJ2">
-        <v>-0.01142766025300308</v>
+        <v>-0.01665572204644499</v>
       </c>
       <c r="AK2">
-        <v>-0.02971254836926479</v>
+        <v>-0.04518950437317786</v>
       </c>
       <c r="AL2">
-        <v>21.4</v>
+        <v>19.4</v>
       </c>
       <c r="AM2">
-        <v>21.4</v>
+        <v>19.4</v>
       </c>
       <c r="AN2">
-        <v>1.627653783342406</v>
+        <v>1.343013698630137</v>
       </c>
       <c r="AO2">
-        <v>8.369158878504674</v>
+        <v>8.685567010309279</v>
       </c>
       <c r="AP2">
-        <v>-0.1170386499727817</v>
+        <v>-0.1528767123287672</v>
       </c>
       <c r="AQ2">
-        <v>8.369158878504674</v>
+        <v>8.685567010309279</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.06559999999999999</v>
+        <v>0.0555</v>
       </c>
       <c r="E3">
-        <v>-0.0646</v>
+        <v>0.122</v>
       </c>
       <c r="G3">
-        <v>0.06247309256158813</v>
+        <v>0.1310240963855422</v>
       </c>
       <c r="H3">
-        <v>0.06247309256158813</v>
+        <v>0.1310240963855422</v>
       </c>
       <c r="I3">
-        <v>0.08567328390337239</v>
+        <v>0.09063037865748709</v>
       </c>
       <c r="J3">
-        <v>0.06834053860500226</v>
+        <v>0.07103858251643462</v>
       </c>
       <c r="K3">
-        <v>102.9</v>
+        <v>137.9</v>
       </c>
       <c r="L3">
-        <v>0.04922267400143507</v>
+        <v>0.07417168674698796</v>
       </c>
       <c r="M3">
-        <v>43.3887</v>
+        <v>146.6</v>
       </c>
       <c r="N3">
-        <v>0.02280135582531925</v>
+        <v>0.08608338226658838</v>
       </c>
       <c r="O3">
-        <v>0.4216588921282798</v>
+        <v>1.06308919506889</v>
       </c>
       <c r="P3">
-        <v>34.2087</v>
+        <v>136.6</v>
       </c>
       <c r="Q3">
-        <v>0.01797714015450103</v>
+        <v>0.08021139166177334</v>
       </c>
       <c r="R3">
-        <v>0.3324460641399417</v>
+        <v>0.9905728788977519</v>
       </c>
       <c r="S3">
-        <v>9.18</v>
+        <v>10</v>
       </c>
       <c r="T3">
-        <v>0.211575825042004</v>
+        <v>0.06821282401091405</v>
       </c>
       <c r="U3">
-        <v>320.5</v>
+        <v>273</v>
       </c>
       <c r="V3">
-        <v>0.1684271375269326</v>
+        <v>0.1603053435114504</v>
       </c>
       <c r="W3">
-        <v>0.1957762557077626</v>
+        <v>0.1979047072330655</v>
       </c>
       <c r="X3">
-        <v>0.07861119274588846</v>
+        <v>0.1238312207094029</v>
       </c>
       <c r="Y3">
-        <v>0.1171650629618741</v>
+        <v>0.07407348652366258</v>
       </c>
       <c r="Z3">
-        <v>4.954965631666271</v>
+        <v>2.753146749592774</v>
       </c>
       <c r="AA3">
-        <v>0.3386250200373482</v>
+        <v>0.1955796425508</v>
       </c>
       <c r="AB3">
-        <v>0.07271814185535347</v>
+        <v>0.1159769106107354</v>
       </c>
       <c r="AC3">
-        <v>0.2659068781819947</v>
+        <v>0.07960273194006463</v>
       </c>
       <c r="AD3">
-        <v>299</v>
+        <v>245.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>299</v>
+        <v>245.1</v>
       </c>
       <c r="AG3">
-        <v>-21.5</v>
+        <v>-27.90000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.135791816158772</v>
+        <v>0.1258148965658847</v>
       </c>
       <c r="AI3">
-        <v>0.2863710372569678</v>
+        <v>0.2752695417789757</v>
       </c>
       <c r="AJ3">
-        <v>-0.01142766025300308</v>
+        <v>-0.01665572204644499</v>
       </c>
       <c r="AK3">
-        <v>-0.02971254836926479</v>
+        <v>-0.04518950437317786</v>
       </c>
       <c r="AL3">
-        <v>21.4</v>
+        <v>19.4</v>
       </c>
       <c r="AM3">
-        <v>21.4</v>
+        <v>19.4</v>
       </c>
       <c r="AN3">
-        <v>1.627653783342406</v>
+        <v>1.343013698630137</v>
       </c>
       <c r="AO3">
-        <v>8.369158878504674</v>
+        <v>8.685567010309279</v>
       </c>
       <c r="AP3">
-        <v>-0.1170386499727817</v>
+        <v>-0.1528767123287672</v>
       </c>
       <c r="AQ3">
-        <v>8.369158878504674</v>
+        <v>8.685567010309279</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/south_africa/south_africa_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/south_africa/south_africa_insurance_prop_cas.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0555</v>
+        <v>0.07185</v>
       </c>
       <c r="E2">
-        <v>0.122</v>
+        <v>0.00205</v>
       </c>
       <c r="G2">
-        <v>0.1310240963855422</v>
+        <v>0.1491125882272322</v>
       </c>
       <c r="H2">
-        <v>0.1310240963855422</v>
+        <v>0.1491125882272322</v>
       </c>
       <c r="I2">
-        <v>0.09063037865748709</v>
+        <v>0.14849585417666</v>
       </c>
       <c r="J2">
-        <v>0.07103858251643462</v>
+        <v>0.1061442374455922</v>
       </c>
       <c r="K2">
-        <v>137.9</v>
+        <v>300</v>
       </c>
       <c r="L2">
-        <v>0.07417168674698796</v>
+        <v>0.1027890084286987</v>
       </c>
       <c r="M2">
-        <v>146.6</v>
+        <v>167.4</v>
       </c>
       <c r="N2">
-        <v>0.08608338226658838</v>
+        <v>0.03155989593152596</v>
       </c>
       <c r="O2">
-        <v>1.06308919506889</v>
+        <v>0.5579999999999999</v>
       </c>
       <c r="P2">
-        <v>136.6</v>
+        <v>151.7</v>
       </c>
       <c r="Q2">
-        <v>0.08021139166177334</v>
+        <v>0.02859997737641869</v>
       </c>
       <c r="R2">
-        <v>0.9905728788977519</v>
+        <v>0.5056666666666666</v>
       </c>
       <c r="S2">
-        <v>10</v>
+        <v>15.7</v>
       </c>
       <c r="T2">
-        <v>0.06821282401091405</v>
+        <v>0.09378733572281962</v>
       </c>
       <c r="U2">
-        <v>273</v>
+        <v>335.7</v>
       </c>
       <c r="V2">
-        <v>0.1603053435114504</v>
+        <v>0.06328946872289884</v>
       </c>
       <c r="W2">
-        <v>0.1979047072330655</v>
+        <v>0.2301450803837099</v>
       </c>
       <c r="X2">
-        <v>0.1238312207094029</v>
+        <v>0.1011311524750418</v>
       </c>
       <c r="Y2">
-        <v>0.07407348652366258</v>
+        <v>0.1290139279086681</v>
       </c>
       <c r="Z2">
-        <v>2.753146749592774</v>
+        <v>2.579613049204091</v>
       </c>
       <c r="AA2">
-        <v>0.1955796425508</v>
+        <v>0.2738980405814065</v>
       </c>
       <c r="AB2">
-        <v>0.1159769106107354</v>
+        <v>0.09835131028842359</v>
       </c>
       <c r="AC2">
-        <v>0.07960273194006463</v>
+        <v>0.1755467302929829</v>
       </c>
       <c r="AD2">
-        <v>245.1</v>
+        <v>238.45</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>245.1</v>
+        <v>238.45</v>
       </c>
       <c r="AG2">
-        <v>-27.90000000000001</v>
+        <v>-97.25000000000006</v>
       </c>
       <c r="AH2">
-        <v>0.1258148965658847</v>
+        <v>0.04302093763813338</v>
       </c>
       <c r="AI2">
-        <v>0.2752695417789757</v>
+        <v>0.1466888130171327</v>
       </c>
       <c r="AJ2">
-        <v>-0.01665572204644499</v>
+        <v>-0.01867696060073557</v>
       </c>
       <c r="AK2">
-        <v>-0.04518950437317786</v>
+        <v>-0.07539636391828512</v>
       </c>
       <c r="AL2">
-        <v>19.4</v>
+        <v>21.12</v>
       </c>
       <c r="AM2">
-        <v>19.4</v>
+        <v>21.12</v>
       </c>
       <c r="AN2">
-        <v>1.343013698630137</v>
+        <v>0.5371705339040325</v>
       </c>
       <c r="AO2">
-        <v>8.685567010309279</v>
+        <v>20.52083333333333</v>
       </c>
       <c r="AP2">
-        <v>-0.1528767123287672</v>
+        <v>-0.2190808740707368</v>
       </c>
       <c r="AQ2">
-        <v>8.685567010309279</v>
+        <v>20.52083333333333</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Santam Ltd (JSE:SNT)</t>
+          <t>OUTsurance Group Limited (JSE:OUT)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,121 +722,255 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0555</v>
+        <v>0.118</v>
       </c>
       <c r="E3">
-        <v>0.122</v>
+        <v>-0.0564</v>
       </c>
       <c r="G3">
-        <v>0.1310240963855422</v>
+        <v>0.1942409880798507</v>
       </c>
       <c r="H3">
-        <v>0.1310240963855422</v>
+        <v>0.1942409880798507</v>
       </c>
       <c r="I3">
-        <v>0.09063037865748709</v>
+        <v>0.1902915410024415</v>
       </c>
       <c r="J3">
-        <v>0.07103858251643462</v>
+        <v>0.1332641075789969</v>
       </c>
       <c r="K3">
-        <v>137.9</v>
+        <v>154.8</v>
       </c>
       <c r="L3">
-        <v>0.07417168674698796</v>
+        <v>0.1111589831968979</v>
       </c>
       <c r="M3">
-        <v>146.6</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="N3">
-        <v>0.08608338226658838</v>
+        <v>0.02138371895683656</v>
       </c>
       <c r="O3">
-        <v>1.06308919506889</v>
+        <v>0.4883720930232557</v>
       </c>
       <c r="P3">
-        <v>136.6</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="Q3">
-        <v>0.08021139166177334</v>
+        <v>0.02138371895683656</v>
       </c>
       <c r="R3">
-        <v>0.9905728788977519</v>
+        <v>0.4883720930232557</v>
       </c>
       <c r="S3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.06821282401091405</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>273</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="V3">
-        <v>0.1603053435114504</v>
+        <v>0.02514566951405782</v>
       </c>
       <c r="W3">
-        <v>0.1979047072330655</v>
+        <v>0.2206070970500214</v>
       </c>
       <c r="X3">
-        <v>0.1238312207094029</v>
+        <v>0.09828494762867344</v>
       </c>
       <c r="Y3">
-        <v>0.07407348652366258</v>
+        <v>0.1223221494213479</v>
       </c>
       <c r="Z3">
-        <v>2.753146749592774</v>
+        <v>2.515943704720782</v>
       </c>
       <c r="AA3">
-        <v>0.1955796425508</v>
+        <v>0.3352849925286102</v>
       </c>
       <c r="AB3">
-        <v>0.1159769106107354</v>
+        <v>0.09824024400296237</v>
       </c>
       <c r="AC3">
-        <v>0.07960273194006463</v>
+        <v>0.2370447485256478</v>
       </c>
       <c r="AD3">
-        <v>245.1</v>
+        <v>4.25</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>245.1</v>
+        <v>4.25</v>
       </c>
       <c r="AG3">
-        <v>-27.90000000000001</v>
+        <v>-84.65000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.1258148965658847</v>
+        <v>0.001200683683415027</v>
       </c>
       <c r="AI3">
-        <v>0.2752695417789757</v>
+        <v>0.005489892139766196</v>
       </c>
       <c r="AJ3">
-        <v>-0.01665572204644499</v>
+        <v>-0.02453089907991017</v>
       </c>
       <c r="AK3">
-        <v>-0.04518950437317786</v>
+        <v>-0.1235315578256111</v>
       </c>
       <c r="AL3">
-        <v>19.4</v>
+        <v>2.12</v>
       </c>
       <c r="AM3">
-        <v>19.4</v>
+        <v>2.12</v>
       </c>
       <c r="AN3">
-        <v>1.343013698630137</v>
+        <v>0.01571164510166359</v>
       </c>
       <c r="AO3">
-        <v>8.685567010309279</v>
+        <v>125</v>
       </c>
       <c r="AP3">
-        <v>-0.1528767123287672</v>
+        <v>-0.3129390018484289</v>
       </c>
       <c r="AQ3">
-        <v>8.685567010309279</v>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Santam Ltd (JSE:SNT)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.0257</v>
+      </c>
+      <c r="E4">
+        <v>0.0605</v>
+      </c>
+      <c r="G4">
+        <v>0.1079292267365662</v>
+      </c>
+      <c r="H4">
+        <v>0.1079292267365662</v>
+      </c>
+      <c r="I4">
+        <v>0.1103538663171691</v>
+      </c>
+      <c r="J4">
+        <v>0.08047847845459095</v>
+      </c>
+      <c r="K4">
+        <v>145.2</v>
+      </c>
+      <c r="L4">
+        <v>0.09515072083879422</v>
+      </c>
+      <c r="M4">
+        <v>91.8</v>
+      </c>
+      <c r="N4">
+        <v>0.05189959294436906</v>
+      </c>
+      <c r="O4">
+        <v>0.6322314049586777</v>
+      </c>
+      <c r="P4">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="Q4">
+        <v>0.04302351876978742</v>
+      </c>
+      <c r="R4">
+        <v>0.5241046831955923</v>
+      </c>
+      <c r="S4">
+        <v>15.7</v>
+      </c>
+      <c r="T4">
+        <v>0.1710239651416122</v>
+      </c>
+      <c r="U4">
+        <v>246.8</v>
+      </c>
+      <c r="V4">
+        <v>0.1395296246042515</v>
+      </c>
+      <c r="W4">
+        <v>0.2396830637173985</v>
+      </c>
+      <c r="X4">
+        <v>0.1039773573214102</v>
+      </c>
+      <c r="Y4">
+        <v>0.1357057063959883</v>
+      </c>
+      <c r="Z4">
+        <v>2.640595258695276</v>
+      </c>
+      <c r="AA4">
+        <v>0.2125110886342028</v>
+      </c>
+      <c r="AB4">
+        <v>0.09846237657388479</v>
+      </c>
+      <c r="AC4">
+        <v>0.114048712060318</v>
+      </c>
+      <c r="AD4">
+        <v>234.2</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>234.2</v>
+      </c>
+      <c r="AG4">
+        <v>-12.60000000000002</v>
+      </c>
+      <c r="AH4">
+        <v>0.1169246130803794</v>
+      </c>
+      <c r="AI4">
+        <v>0.2750763448437867</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.007174581482746853</v>
+      </c>
+      <c r="AK4">
+        <v>-0.02084022494211052</v>
+      </c>
+      <c r="AL4">
+        <v>19</v>
+      </c>
+      <c r="AM4">
+        <v>19</v>
+      </c>
+      <c r="AN4">
+        <v>1.350634371395617</v>
+      </c>
+      <c r="AO4">
+        <v>8.863157894736842</v>
+      </c>
+      <c r="AP4">
+        <v>-0.07266435986159182</v>
+      </c>
+      <c r="AQ4">
+        <v>8.863157894736842</v>
       </c>
     </row>
   </sheetData>
